--- a/artfynd/A 28849-2024 artfynd.xlsx
+++ b/artfynd/A 28849-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89847964</v>
+        <v>89847968</v>
       </c>
       <c r="B2" t="n">
-        <v>56538</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -723,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>373654.2242295743</v>
+        <v>373654</v>
       </c>
       <c r="R2" t="n">
-        <v>6481721.128426892</v>
+        <v>6481721</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -788,22 +783,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Martin Kindgren, Lennart Carlsson, Sofie Johansson</t>
+          <t>Martin Kindgren, Lennart Carlsson, Sofie Kindgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>98232709</v>
+        <v>89847964</v>
       </c>
       <c r="B3" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58112</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,26 +801,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -843,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>373654.2242295743</v>
+        <v>373654</v>
       </c>
       <c r="R3" t="n">
-        <v>6481721.128426892</v>
+        <v>6481721</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -873,22 +863,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-01-21</t>
+          <t>2020-12-31</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-01-21</t>
+          <t>2020-12-31</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +898,240 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
+          <t>Martin Kindgren, Lennart Carlsson, Sofie Kindgren</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>98232709</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Tådene,Lidköping, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>373654</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6481721</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Lidköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Tådene</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-01-21</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-01-21</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Martin Kindgren</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Martin Kindgren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>98232717</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Tådene,Lidköping, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>373654</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6481721</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lidköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Tådene</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-01-21</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-01-21</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Martin Kindgren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Martin Kindgren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28849-2024 artfynd.xlsx
+++ b/artfynd/A 28849-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89847968</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89847964</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1017,6 +1032,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98232709</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1132,8 +1152,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98232717</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>